--- a/registration_forms/049_running_tournament_registration_form--registration_forms.xlsx
+++ b/registration_forms/049_running_tournament_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>participant name</t>
+          <t>Participant Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>participant_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>participant_phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,110 +589,110 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact email</t>
+          <t>Team Members</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>team_tier</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact phone</t>
+          <t>Team Tier</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>team_members</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>team members</t>
+          <t>Event Date</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>team_tier</t>
+          <t>event_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>team tier</t>
+          <t>Event Time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>division</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>division</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>age group</t>
+          <t>Age Group</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,82 +755,82 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>shirt size</t>
+          <t>Shirt Size</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>participant_number</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>event date</t>
+          <t>Participant Number</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>division</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>event time</t>
+          <t>Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>event_tier</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Event Tier</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,248 +842,87 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>participant_number</t>
+          <t>confirm_participant_name</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>participant number</t>
+          <t>Confirm Participant Name</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>team_tier</t>
+          <t>confirm_team_members</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>team tier</t>
+          <t>Confirm Team Members</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>division</t>
+          <t>confirm_event_date</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>division</t>
+          <t>Confirm Event Date</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>age_group</t>
+          <t>confirm_age_group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>age group</t>
+          <t>Confirm Age Group</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>shirt_size</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>shirt size</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>event date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>event_time</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>event time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_number</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>participant number</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>event_tier</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>event tier</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1177,85 +1016,85 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>division_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>division_1</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>division 1</t>
+          <t>18-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>division_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>division_2</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>division 2</t>
+          <t>30-39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>division_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>division_3</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>division 3</t>
+          <t>40-49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>division_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>division_4</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>division 4</t>
+          <t>50-59</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>division_choices</t>
+          <t>age_group_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>division_5</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>division 5</t>
+          <t>60-69</t>
         </is>
       </c>
     </row>
@@ -1267,206 +1106,206 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18-29</t>
+          <t>70+</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18-29</t>
+          <t>70+</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>shirt_size_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>age_group_choices</t>
+          <t>shirt_size_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gender_choices</t>
+          <t>shirt_size_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gender_choices</t>
+          <t>division_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>division_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Division 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gender_choices</t>
+          <t>division_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>non-binary</t>
+          <t>division_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>non-binary</t>
+          <t>Division 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>shirt_size_choices</t>
+          <t>division_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>division_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>Division 3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>shirt_size_choices</t>
+          <t>division_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>division_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Division 4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shirt_size_choices</t>
+          <t>division_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>division_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>Division 5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>team_tier_choices</t>
+          <t>event_tier_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1322,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>team_tier_choices</t>
+          <t>event_tier_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1339,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>team_tier_choices</t>
+          <t>event_tier_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1509,346 +1348,6 @@
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>3rd place</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>division_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>division_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>division 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>division_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>division_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>division 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>division_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>division_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>division 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>division_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>division_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>division 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>division_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>division_5</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>division 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>age_group_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>18-29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>18-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>age_group_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>age_group_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>age_group_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>age_group_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>age_group_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>70+</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>70+</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>gender_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>gender_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>gender_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>non-binary</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>non-binary</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>shirt_size_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>shirt_size_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>shirt_size_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>event_tier_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1st_place</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1st place</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>event_tier_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2nd_place</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2nd place</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>event_tier_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3rd_place</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
         <is>
           <t>3rd place</t>
         </is>
